--- a/doc/5、开发文档/协议转换单元DLT64点表.xlsx
+++ b/doc/5、开发文档/协议转换单元DLT64点表.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\5、开发文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14002FE-0E38-4E27-BACB-7EC248C74080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECFADEC-6EA0-43CF-9743-95831ADBD573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="参变量" sheetId="4" r:id="rId1"/>
+    <sheet name="档案与协议库" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="214">
   <si>
     <t>00</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -744,6 +744,130 @@
 TTTT：0~3Bit：数据类型，4~7bit：字节序，8~11Bit：小数位数，12~15Bit：预留
 LLLLLLLL：特征值下限
 HHHHHHHH：特征值上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BBBBBBBB
+TT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4
+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RS485-Ⅰ参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RS485-Ⅱ参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45-1-Ⅰ参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45-1-Ⅱ参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45-2-Ⅰ参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45-2-Ⅱ参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>载波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波特率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校验格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BBBBBBBB：16进制，非BCD码，小端
+TT：校验格式：1=8,N,1; 2=8,O,1 3=8,E,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轮询时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复出厂设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0F</t>
+  </si>
+  <si>
+    <t>XXXX.XXXX</t>
+  </si>
+  <si>
+    <t>XXXX.XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>维度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5~3600s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NNNN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写1重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写1清除所有事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写1恢复出厂设置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -892,7 +1016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -954,68 +1078,132 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -1321,6 +1509,539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C9C05F-D0FC-4B32-8A10-0D5248EE0CE7}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="9" style="42"/>
+    <col min="5" max="5" width="26.625" style="43" customWidth="1"/>
+    <col min="6" max="6" width="9" style="43"/>
+    <col min="7" max="7" width="24.375" style="43" customWidth="1"/>
+    <col min="8" max="8" width="9" style="43"/>
+    <col min="9" max="9" width="9" style="43" customWidth="1"/>
+    <col min="10" max="10" width="33" style="43" customWidth="1"/>
+    <col min="11" max="11" width="51.25" style="44" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="43"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="40"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="28"/>
+      <c r="J2" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="39"/>
+      <c r="K3" s="31"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K6" s="29"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7" s="29"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K8" s="29"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K9" s="29"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K10" s="29"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K11" s="29"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="46">
+        <v>2</v>
+      </c>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="K13" s="47" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="46">
+        <v>1</v>
+      </c>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="K14" s="47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="46">
+        <v>1</v>
+      </c>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="47" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="46">
+        <v>1</v>
+      </c>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="K16" s="47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="K20" s="47"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="K21" s="47"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="K22" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A4:A11"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="F4:F11"/>
+    <mergeCell ref="H4:H11"/>
+    <mergeCell ref="I4:I11"/>
+    <mergeCell ref="K5:K11"/>
+    <mergeCell ref="E4:E11"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:K2 A3:F3 H3:J3">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="扩展">
+      <formula>NOT(ISERROR(SEARCH("扩展",A2)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G11">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:I4">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="扩展">
+      <formula>NOT(ISERROR(SEARCH("扩展",H4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:I4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:E4 D5:D11 A2:K2 A3:F3 H3:J3 K4:K5 J4:J11">
+    <cfRule type="colorScale" priority="143">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:D20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{073B0526-4720-496A-823D-3ED4F9E498DD}">
   <dimension ref="A2:O88"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.2"/>
@@ -1340,26 +2061,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="23" t="s">
+      <c r="I2" s="28"/>
+      <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="30" t="s">
@@ -1379,26 +2100,26 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="25"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="27"/>
       <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="39"/>
       <c r="K3" s="31"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="21" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1407,14 +2128,14 @@
       <c r="E4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="25" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="33" t="s">
+      <c r="H4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="23" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1423,19 +2144,19 @@
       <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="35"/>
+      <c r="F5" s="26"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="1" t="s">
         <v>46</v>
       </c>
@@ -1444,195 +2165,195 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="26"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
       <c r="J6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="K6" s="29"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="26"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
       <c r="J7" s="1" t="s">
         <v>48</v>
       </c>
       <c r="K7" s="29"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="26"/>
       <c r="G8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="K8" s="29"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="26"/>
       <c r="G9" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
       <c r="J9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K9" s="29"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="26"/>
       <c r="G10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
       <c r="J10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K10" s="29"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="26"/>
       <c r="G11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="1" t="s">
         <v>52</v>
       </c>
       <c r="K11" s="29"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="26"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
       <c r="J12" s="1" t="s">
         <v>53</v>
       </c>
       <c r="K12" s="29"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="26"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
       <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K13" s="29"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="26"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="1" t="s">
         <v>55</v>
       </c>
       <c r="K14" s="29"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="26"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="K15" s="29"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
       <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="35"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="26"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
       <c r="J16" s="1" t="s">
         <v>57</v>
       </c>
@@ -1649,19 +2370,19 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="34" t="s">
         <v>178</v>
       </c>
       <c r="F18" s="18">
@@ -1670,19 +2391,19 @@
       <c r="G18" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="33" t="s">
+      <c r="H18" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I18" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="33" t="s">
+      <c r="J18" s="23" t="s">
         <v>26</v>
       </c>
       <c r="K18" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="L18" s="24"/>
+      <c r="L18" s="25"/>
       <c r="M18" s="1" t="s">
         <v>147</v>
       </c>
@@ -1694,23 +2415,23 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="38"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="35"/>
       <c r="F19" s="19">
         <v>2</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
       <c r="K19" s="29"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="24" t="s">
+      <c r="L19" s="26"/>
+      <c r="M19" s="25" t="s">
         <v>150</v>
       </c>
       <c r="N19" s="1">
@@ -1721,23 +2442,23 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="38"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="35"/>
       <c r="F20" s="19">
         <v>14</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
       <c r="K20" s="29"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
@@ -1746,23 +2467,23 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="38"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="35"/>
       <c r="F21" s="19">
         <v>6</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
       <c r="K21" s="29"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
       <c r="N21" s="1">
         <v>2</v>
       </c>
@@ -1771,23 +2492,23 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="38"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="35"/>
       <c r="F22" s="19">
         <v>6</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
       <c r="K22" s="29"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
       <c r="N22" s="1">
         <v>3</v>
       </c>
@@ -1796,23 +2517,23 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="38"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="35"/>
       <c r="F23" s="19">
         <v>6</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
       <c r="K23" s="29"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
       <c r="N23" s="1">
         <v>4</v>
       </c>
@@ -1821,23 +2542,23 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="38"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="35"/>
       <c r="F24" s="19">
         <v>6</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
       <c r="K24" s="29"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
       <c r="N24" s="1">
         <v>5</v>
       </c>
@@ -1846,23 +2567,23 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="38"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
       <c r="F25" s="19">
         <v>6</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
       <c r="K25" s="29"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
       <c r="N25" s="1">
         <v>6</v>
       </c>
@@ -1871,23 +2592,23 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="38"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
       <c r="F26" s="19">
         <v>6</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
       <c r="K26" s="29"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
       <c r="N26" s="1">
         <v>7</v>
       </c>
@@ -1896,23 +2617,23 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="38"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="35"/>
       <c r="F27" s="19">
         <v>6</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
       <c r="K27" s="29"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
       <c r="N27" s="1">
         <v>8</v>
       </c>
@@ -1921,23 +2642,23 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="38"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="35"/>
       <c r="F28" s="19">
         <v>6</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
       <c r="K28" s="29"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
       <c r="N28" s="1">
         <v>9</v>
       </c>
@@ -1946,23 +2667,23 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="38"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="35"/>
       <c r="F29" s="19">
         <v>6</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
       <c r="K29" s="29"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
       <c r="N29" s="1">
         <v>10</v>
       </c>
@@ -1971,23 +2692,23 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="38"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="35"/>
       <c r="F30" s="19">
         <v>6</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
       <c r="K30" s="29"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
       <c r="N30" s="1">
         <v>11</v>
       </c>
@@ -1996,23 +2717,23 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="38"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="35"/>
       <c r="F31" s="19">
         <v>6</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
       <c r="K31" s="29"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="25"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="27"/>
       <c r="N31" s="1" t="s">
         <v>180</v>
       </c>
@@ -2021,23 +2742,23 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="38"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="35"/>
       <c r="F32" s="19">
         <v>6</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
       <c r="K32" s="29"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="24" t="s">
+      <c r="L32" s="26"/>
+      <c r="M32" s="25" t="s">
         <v>162</v>
       </c>
       <c r="N32" s="1">
@@ -2048,23 +2769,23 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="38"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="35"/>
       <c r="F33" s="19">
         <v>6</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
       <c r="K33" s="29"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
@@ -2073,23 +2794,23 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="38"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="35"/>
       <c r="F34" s="19">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
       <c r="K34" s="29"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
       <c r="N34" s="1">
         <v>2</v>
       </c>
@@ -2098,23 +2819,23 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="38"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="35"/>
       <c r="F35" s="19">
         <v>6</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
       <c r="K35" s="29"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="35"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
       <c r="N35" s="1">
         <v>3</v>
       </c>
@@ -2123,23 +2844,23 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="38"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="35"/>
       <c r="F36" s="19">
         <v>6</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
       <c r="K36" s="29"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="25"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="27"/>
       <c r="N36" s="1" t="s">
         <v>167</v>
       </c>
@@ -2148,23 +2869,23 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="38"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="35"/>
       <c r="F37" s="19">
         <v>6</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
       <c r="K37" s="29"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="24" t="s">
+      <c r="L37" s="26"/>
+      <c r="M37" s="25" t="s">
         <v>168</v>
       </c>
       <c r="N37" s="1">
@@ -2175,23 +2896,23 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="38"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="35"/>
       <c r="F38" s="19">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
       <c r="K38" s="29"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
       <c r="N38" s="1">
         <v>1</v>
       </c>
@@ -2200,23 +2921,23 @@
       </c>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="38"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="35"/>
       <c r="F39" s="19">
         <v>6</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
       <c r="K39" s="29"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
       <c r="N39" s="1">
         <v>2</v>
       </c>
@@ -2225,23 +2946,23 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="38"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="35"/>
       <c r="F40" s="19">
         <v>6</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
       <c r="K40" s="29"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
       <c r="N40" s="1">
         <v>3</v>
       </c>
@@ -2250,23 +2971,23 @@
       </c>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="38"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="35"/>
       <c r="F41" s="19">
         <v>6</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
       <c r="K41" s="29"/>
-      <c r="L41" s="35"/>
-      <c r="M41" s="35"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1">
         <v>4</v>
       </c>
@@ -2275,23 +2996,23 @@
       </c>
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="38"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="35"/>
       <c r="F42" s="19">
         <v>6</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
       <c r="K42" s="29"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="35"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
       <c r="N42" s="1">
         <v>5</v>
       </c>
@@ -2300,23 +3021,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="38"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="35"/>
       <c r="F43" s="19">
         <v>6</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
       <c r="K43" s="29"/>
-      <c r="L43" s="35"/>
-      <c r="M43" s="25"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="27"/>
       <c r="N43" s="1" t="s">
         <v>175</v>
       </c>
@@ -2325,22 +3046,22 @@
       </c>
     </row>
     <row r="44" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="38"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="35"/>
       <c r="F44" s="19">
         <v>8</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
       <c r="K44" s="29"/>
-      <c r="L44" s="35"/>
+      <c r="L44" s="26"/>
       <c r="M44" s="1" t="s">
         <v>176</v>
       </c>
@@ -2350,119 +3071,119 @@
       <c r="O44" s="1"/>
     </row>
     <row r="45" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="38"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="35"/>
       <c r="F45" s="19">
         <v>8</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
       <c r="K45" s="29"/>
-      <c r="L45" s="35"/>
+      <c r="L45" s="26"/>
     </row>
     <row r="46" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="38"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="35"/>
       <c r="F46" s="19">
         <v>6</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
       <c r="K46" s="29"/>
-      <c r="L46" s="35"/>
+      <c r="L46" s="26"/>
     </row>
     <row r="47" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="38"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="35"/>
       <c r="F47" s="19">
         <v>6</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
       <c r="K47" s="29"/>
-      <c r="L47" s="35"/>
+      <c r="L47" s="26"/>
     </row>
     <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="38"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="35"/>
       <c r="F48" s="19">
         <v>6</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
       <c r="K48" s="29"/>
-      <c r="L48" s="35"/>
+      <c r="L48" s="26"/>
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="38"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="35"/>
       <c r="F49" s="19">
         <v>6</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
       <c r="K49" s="29"/>
-      <c r="L49" s="35"/>
+      <c r="L49" s="26"/>
     </row>
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="38"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="35"/>
       <c r="F50" s="19">
         <v>6</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
       <c r="K50" s="29"/>
-      <c r="L50" s="35"/>
+      <c r="L50" s="26"/>
     </row>
     <row r="51" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
-      <c r="E51" s="39"/>
+      <c r="E51" s="36"/>
       <c r="F51" s="19">
         <v>6</v>
       </c>
@@ -2488,7 +3209,7 @@
       <c r="D52" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="28" t="s">
         <v>38</v>
       </c>
       <c r="F52" s="1">
@@ -2518,7 +3239,7 @@
       <c r="D53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="21"/>
+      <c r="E53" s="28"/>
       <c r="F53" s="1">
         <v>238</v>
       </c>
@@ -2546,7 +3267,7 @@
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="21"/>
+      <c r="E54" s="28"/>
       <c r="F54" s="1">
         <v>238</v>
       </c>
@@ -2574,7 +3295,7 @@
       <c r="D55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="21"/>
+      <c r="E55" s="28"/>
       <c r="F55" s="1">
         <v>238</v>
       </c>
@@ -2602,7 +3323,7 @@
       <c r="D56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E56" s="21"/>
+      <c r="E56" s="28"/>
       <c r="F56" s="1">
         <v>238</v>
       </c>
@@ -2630,7 +3351,7 @@
       <c r="D57" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="21"/>
+      <c r="E57" s="28"/>
       <c r="F57" s="1">
         <v>238</v>
       </c>
@@ -2658,7 +3379,7 @@
       <c r="D58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="21"/>
+      <c r="E58" s="28"/>
       <c r="F58" s="1">
         <v>238</v>
       </c>
@@ -2686,7 +3407,7 @@
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="21"/>
+      <c r="E59" s="28"/>
       <c r="F59" s="1">
         <v>238</v>
       </c>
@@ -2715,7 +3436,7 @@
       <c r="D60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="21"/>
+      <c r="E60" s="28"/>
       <c r="F60" s="1">
         <v>238</v>
       </c>
@@ -2743,7 +3464,7 @@
       <c r="D61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="21"/>
+      <c r="E61" s="28"/>
       <c r="F61" s="1">
         <v>238</v>
       </c>
@@ -2772,7 +3493,7 @@
       <c r="D62" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="21"/>
+      <c r="E62" s="28"/>
       <c r="F62" s="1">
         <v>238</v>
       </c>
@@ -2800,7 +3521,7 @@
       <c r="D63" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E63" s="21"/>
+      <c r="E63" s="28"/>
       <c r="F63" s="1">
         <v>238</v>
       </c>
@@ -2828,7 +3549,7 @@
       <c r="D64" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="21"/>
+      <c r="E64" s="28"/>
       <c r="F64" s="1">
         <v>238</v>
       </c>
@@ -2856,7 +3577,7 @@
       <c r="D65" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E65" s="21"/>
+      <c r="E65" s="28"/>
       <c r="F65" s="1">
         <v>238</v>
       </c>
@@ -2885,7 +3606,7 @@
       <c r="D66" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="21"/>
+      <c r="E66" s="28"/>
       <c r="F66" s="1">
         <v>238</v>
       </c>
@@ -2913,7 +3634,7 @@
       <c r="D67" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E67" s="21"/>
+      <c r="E67" s="28"/>
       <c r="F67" s="1">
         <v>238</v>
       </c>
@@ -2941,7 +3662,7 @@
       <c r="D68" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E68" s="21"/>
+      <c r="E68" s="28"/>
       <c r="F68" s="1">
         <v>238</v>
       </c>
@@ -2969,7 +3690,7 @@
       <c r="D69" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E69" s="21"/>
+      <c r="E69" s="28"/>
       <c r="F69" s="1">
         <v>238</v>
       </c>
@@ -2997,7 +3718,7 @@
       <c r="D70" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E70" s="21"/>
+      <c r="E70" s="28"/>
       <c r="F70" s="1">
         <v>238</v>
       </c>
@@ -3025,7 +3746,7 @@
       <c r="D71" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E71" s="21"/>
+      <c r="E71" s="28"/>
       <c r="F71" s="1">
         <v>238</v>
       </c>
@@ -3053,7 +3774,7 @@
       <c r="D72" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E72" s="21"/>
+      <c r="E72" s="28"/>
       <c r="F72" s="1">
         <v>238</v>
       </c>
@@ -3081,7 +3802,7 @@
       <c r="D73" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E73" s="21"/>
+      <c r="E73" s="28"/>
       <c r="F73" s="1">
         <v>238</v>
       </c>
@@ -3109,7 +3830,7 @@
       <c r="D74" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E74" s="21"/>
+      <c r="E74" s="28"/>
       <c r="F74" s="1">
         <v>238</v>
       </c>
@@ -3137,7 +3858,7 @@
       <c r="D75" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E75" s="21"/>
+      <c r="E75" s="28"/>
       <c r="F75" s="1">
         <v>238</v>
       </c>
@@ -3165,7 +3886,7 @@
       <c r="D76" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E76" s="21"/>
+      <c r="E76" s="28"/>
       <c r="F76" s="1">
         <v>238</v>
       </c>
@@ -3193,7 +3914,7 @@
       <c r="D77" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="21"/>
+      <c r="E77" s="28"/>
       <c r="F77" s="1">
         <v>238</v>
       </c>
@@ -3221,7 +3942,7 @@
       <c r="D78" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="28"/>
       <c r="F78" s="1">
         <v>238</v>
       </c>
@@ -3249,7 +3970,7 @@
       <c r="D79" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E79" s="21"/>
+      <c r="E79" s="28"/>
       <c r="F79" s="1">
         <v>238</v>
       </c>
@@ -3277,7 +3998,7 @@
       <c r="D80" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E80" s="21"/>
+      <c r="E80" s="28"/>
       <c r="F80" s="1">
         <v>238</v>
       </c>
@@ -3305,7 +4026,7 @@
       <c r="D81" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E81" s="21"/>
+      <c r="E81" s="28"/>
       <c r="F81" s="1">
         <v>238</v>
       </c>
@@ -3333,7 +4054,7 @@
       <c r="D82" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E82" s="21"/>
+      <c r="E82" s="28"/>
       <c r="F82" s="1">
         <v>238</v>
       </c>
@@ -3361,7 +4082,7 @@
       <c r="D83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E83" s="21"/>
+      <c r="E83" s="28"/>
       <c r="F83" s="1">
         <v>238</v>
       </c>
@@ -3389,7 +4110,7 @@
       <c r="D84" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E84" s="21"/>
+      <c r="E84" s="28"/>
       <c r="F84" s="1">
         <v>238</v>
       </c>
@@ -3417,7 +4138,7 @@
       <c r="D85" s="1">
         <v>23</v>
       </c>
-      <c r="E85" s="21"/>
+      <c r="E85" s="28"/>
       <c r="F85" s="1">
         <v>238</v>
       </c>
@@ -3445,7 +4166,7 @@
       <c r="D86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E86" s="21"/>
+      <c r="E86" s="28"/>
       <c r="F86" s="1">
         <v>238</v>
       </c>
@@ -3473,7 +4194,7 @@
       <c r="D87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E87" s="21"/>
+      <c r="E87" s="28"/>
       <c r="F87" s="1">
         <v>238</v>
       </c>
@@ -3518,12 +4239,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D18:D50"/>
-    <mergeCell ref="J18:J50"/>
-    <mergeCell ref="L18:L50"/>
-    <mergeCell ref="M19:M31"/>
-    <mergeCell ref="M32:M36"/>
-    <mergeCell ref="M37:M43"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="A4:A16"/>
+    <mergeCell ref="B4:B16"/>
+    <mergeCell ref="C4:C16"/>
+    <mergeCell ref="C18:C50"/>
+    <mergeCell ref="B18:B50"/>
+    <mergeCell ref="A18:A50"/>
     <mergeCell ref="E52:E87"/>
     <mergeCell ref="K5:K16"/>
     <mergeCell ref="K2:K3"/>
@@ -3535,18 +4262,12 @@
     <mergeCell ref="I4:I16"/>
     <mergeCell ref="E5:E16"/>
     <mergeCell ref="E18:E51"/>
-    <mergeCell ref="A4:A16"/>
-    <mergeCell ref="B4:B16"/>
-    <mergeCell ref="C4:C16"/>
-    <mergeCell ref="C18:C50"/>
-    <mergeCell ref="B18:B50"/>
-    <mergeCell ref="A18:A50"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D18:D50"/>
+    <mergeCell ref="J18:J50"/>
+    <mergeCell ref="L18:L50"/>
+    <mergeCell ref="M19:M31"/>
+    <mergeCell ref="M32:M36"/>
+    <mergeCell ref="M37:M43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A4:E4 K60 A18:E18 D5:D17 A2:K2 K52:K56 A3:F3 H3:J3 K17 K4:K5 E52 D52:D84 D86:D88 A52:C88 K62 J4:J18 J52:J88">
@@ -3726,185 +4447,4 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AD079A-0118-427D-845E-851C9BA2D673}">
-  <dimension ref="A1:A37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>